--- a/report_forms/043_sleep_disturbance_report_form--report_forms.xlsx
+++ b/report_forms/043_sleep_disturbance_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,7 +730,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -996,17 +996,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>disturbances_choices</t>
+          <t>sleep_location_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sleepwalking</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sleepwalking</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
@@ -1018,12 +1018,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>bed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Bed</t>
         </is>
       </c>
     </row>
@@ -1035,12 +1035,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>bed</t>
+          <t>hotel</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bed</t>
+          <t>Hotel</t>
         </is>
       </c>
     </row>
@@ -1052,12 +1052,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hotel</t>
+          <t>clinic</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hotel</t>
+          <t>Clinic</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>clinic</t>
+          <t>lab</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Clinic</t>
+          <t>Lab</t>
         </is>
       </c>
     </row>
@@ -1086,29 +1086,29 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>lab</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Lab</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>sleep_location_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>chatjimmy</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>chatjimmy</t>
         </is>
       </c>
     </row>
@@ -1120,12 +1120,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>chatjimmy1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>chatjimmy</t>
+          <t>chatjimmy1</t>
         </is>
       </c>
     </row>
@@ -1137,27 +1137,10 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>chatjimmy1</t>
+          <t>chatjimmy2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
-        <is>
-          <t>chatjimmy1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>assigned_tool_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>chatjimmy2</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
         <is>
           <t>chatjimmy2</t>
         </is>
